--- a/PTBR/Lang/PTBR/Game/Block.xlsx
+++ b/PTBR/Lang/PTBR/Game/Block.xlsx
@@ -437,7 +437,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H207"/>
+  <dimension ref="A1:H222"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col collapsed="1" width="16" customWidth="1" min="1" max="1"/>
@@ -517,7 +517,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Bloco de Terra</t>
+          <t>bloco de terra</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -544,7 +544,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Cerca de Madeira</t>
+          <t>cerca de madeira</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -571,7 +571,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Rampa Natural</t>
+          <t>rampa natural</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -598,7 +598,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Escadas de Pedra</t>
+          <t>escada de pedra</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -625,7 +625,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Degrau Natural</t>
+          <t>degrau natural</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -652,7 +652,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Rampa de Pedra</t>
+          <t>rampa de pedra</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -679,7 +679,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Telhado</t>
+          <t>laje</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Bloco de Tronco</t>
+          <t>bloco de tronco</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -733,7 +733,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Bloco de Pedra</t>
+          <t>bloco de pedra</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Bloco decorativo</t>
+          <t>bloco de decoração</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>degrau de Pedra</t>
+          <t>degrau de pedra</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -814,7 +814,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Bloco de Vidro</t>
+          <t>bloco de vidro</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -841,7 +841,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Andaime</t>
+          <t>andaime</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -856,7 +856,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Um ponto de apoio indispensável na construção.</t>
+          <t>建筑中不可缺少的立足点。</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -878,7 +878,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Bloco de Vidro</t>
+          <t>bloco de vidro</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -905,7 +905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Bloco de Espelho</t>
+          <t>bloco de espelho</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Bloco de Pedra</t>
+          <t>bloco de pedra</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -959,7 +959,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Bloco de Madeiras Reforçada</t>
+          <t>bloco de tábuas reforçadas</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Bloco de Magma</t>
+          <t>bloco de magma</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1013,7 +1013,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Bloco de Pedra</t>
+          <t>bloco de pedra</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Bloco de Pedra</t>
+          <t>bloco de pedra</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1067,7 +1067,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Bloco de Pedra</t>
+          <t>bloco de pedra</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Bloco de Madeira</t>
+          <t>bloco de madeira</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1121,7 +1121,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Bloco de Espelho</t>
+          <t>bloco de espelho</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Bloco Fofo</t>
+          <t>bloco fofinho</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Bloco de Órgão</t>
+          <t>bloco orgânico</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Cerca de Metal</t>
+          <t>cerca de metal</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1229,7 +1229,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Cerca de Madeira</t>
+          <t>cerca de madeira</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Andaime</t>
+          <t>andaime</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1271,7 +1271,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Um ponto de apoio indispensável na construção.</t>
+          <t>建筑中不可缺少的立足点。</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Rampa de Madeiras</t>
+          <t>rampa de tábuas</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Bloco de Madeiras</t>
+          <t>bloco de tábuas</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Bloco de Madeiras</t>
+          <t>bloco de tábuas</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1374,7 +1374,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Bloco de Madeiras</t>
+          <t>bloco de tábuas</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1401,7 +1401,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Bloco de Areia</t>
+          <t>bloco de areia</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Bloco de Palha</t>
+          <t>bloco de palha</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1455,7 +1455,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Bloco de Gelo</t>
+          <t>bloco de gelo</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Bloco de Neve</t>
+          <t>bloco de neve</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Telhado</t>
+          <t>laje</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Telhado</t>
+          <t>laje</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Telhado</t>
+          <t>laje</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1590,7 +1590,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Telhado</t>
+          <t>laje</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Telhado</t>
+          <t>laje</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1644,7 +1644,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Cerca de Madeira</t>
+          <t>cerca de madeira</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1671,7 +1671,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Cerca de Metal</t>
+          <t>cerca de metal</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1698,7 +1698,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Cerca de Madeira</t>
+          <t>cerca de madeira</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1725,7 +1725,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Escada</t>
+          <t>escada de mão</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1752,7 +1752,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Escadas de Madeiras</t>
+          <t>escada de tábuas</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Parede de Madeiras Espessa</t>
+          <t>parede de tábuas grossas</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -1806,7 +1806,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Parede de Pedra</t>
+          <t>parede de pedra</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Parede de Tijolo</t>
+          <t>parede de tijolos</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -1860,7 +1860,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Bloco de Tijolo</t>
+          <t>bloco de tijolos</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Parede de Tronco</t>
+          <t>parede de troncos</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Parede de Cristal</t>
+          <t>parede de cristal</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -1941,7 +1941,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Bloco de Água</t>
+          <t>bloco de água</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -1968,7 +1968,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Parede de Palha</t>
+          <t>parede de palha</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -1995,7 +1995,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Parede de Pedra</t>
+          <t>parede de pedra</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -2022,7 +2022,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Parede de Madeiras</t>
+          <t>parede de tábuas</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2049,7 +2049,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Parede Arqueada</t>
+          <t>parede em arco</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -2076,7 +2076,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Parede Arqueada</t>
+          <t>parede em arco</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -2103,7 +2103,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Parede Arqueada</t>
+          <t>parede em arco</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2130,7 +2130,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Cerca de Saco de Areia</t>
+          <t>cerca de sacos de areia</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -2157,7 +2157,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Parede Simples</t>
+          <t>parede simples</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Parede Simples</t>
+          <t>parede simples</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Parede Simples</t>
+          <t>parede simples</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -2238,7 +2238,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Parede de Tijolo</t>
+          <t>parede de tijolos</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Cerca de Madeira</t>
+          <t>cerca de madeira</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -2292,7 +2292,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Cerca de Madeira</t>
+          <t>cerca de madeira</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -2319,7 +2319,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Pilar de Madeira</t>
+          <t>pilar de madeira</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -2346,7 +2346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Pilar de Tijolo</t>
+          <t>pilar de tijolos</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -2373,7 +2373,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Pilar de Madeira</t>
+          <t>pilar de madeira</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -2400,7 +2400,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Pilar de Cristal</t>
+          <t>pilar de cristal</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -2427,7 +2427,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Pilar de Pedra</t>
+          <t>pilar de pedra</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -2454,7 +2454,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Pilar de Pedra</t>
+          <t>pilar de pedra</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Pilar de Madeira</t>
+          <t>pilar de madeira</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Pilar de Pedra</t>
+          <t>pilar de pedra</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -2535,7 +2535,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Pilar de Madeira</t>
+          <t>pilar de madeira</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Pilar de Pedra</t>
+          <t>pilar de pedra</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -2589,7 +2589,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Pilar Arqueado</t>
+          <t>pilar em arco</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -2616,7 +2616,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Pilar Arqueado</t>
+          <t>pilar em arco</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -2643,7 +2643,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Pilar Arqueado</t>
+          <t>pilar em arco</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -2670,7 +2670,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Pilar de Madeira</t>
+          <t>pilar de madeira</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Pilar de Pedra</t>
+          <t>pilar de pedra</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -2724,7 +2724,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Pilar de Pedra</t>
+          <t>pilar de pedra</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -2751,7 +2751,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Pilar de Saco de Areia</t>
+          <t>pilar de sacos de areia</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -2778,7 +2778,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Pilar Simples</t>
+          <t>pilar simples</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -2805,7 +2805,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Pilar Simples</t>
+          <t>pilar simples</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -2832,7 +2832,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Pilar Simples</t>
+          <t>pilar simples</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -2859,7 +2859,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Pilar de Tijolo</t>
+          <t>pilar de tijolos</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -2886,7 +2886,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Parede de Prisão</t>
+          <t>parede de prisão</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -2913,7 +2913,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Parede de Madeiras Espessa</t>
+          <t>parede de tábuas grossas</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -2940,7 +2940,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Parede de Madeiras Espessa</t>
+          <t>parede de tábuas grossas</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -2967,7 +2967,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Parede Luminosa</t>
+          <t>parede de Lumiest</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -2994,7 +2994,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Parede de Madeiras</t>
+          <t>parede de tábuas</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -3021,7 +3021,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Cerca de Grama</t>
+          <t>cerca de grama</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Cerca de Grama</t>
+          <t>cerca de grama</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Cerca de Estaca</t>
+          <t>cerca de estacas</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -3102,7 +3102,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Parede de Cinza</t>
+          <t>parede de cinzas</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -3129,7 +3129,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Bloco de Cinza</t>
+          <t>bloco de cinzas</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Parede de Saco de Areia</t>
+          <t>parede de sacos de areia</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -3183,7 +3183,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Meia-Escada Natural</t>
+          <t>meia-escada natural</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -3210,7 +3210,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Meia-Escada de Madeiras</t>
+          <t>meia-escada de tábuas</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -3237,7 +3237,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Meia-Escada de Madeiras</t>
+          <t>meia-escada de tábuas</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -3264,7 +3264,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Parede Moderna</t>
+          <t>parede moderna</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -3291,7 +3291,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Parede Moderna</t>
+          <t>parede moderna</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -3318,7 +3318,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Parede Moderna</t>
+          <t>parede moderna</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -3345,7 +3345,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Parede Moderna</t>
+          <t>parede moderna</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -3372,7 +3372,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Escada de Pedra</t>
+          <t>escada de pedra</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -3399,7 +3399,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Meia-Escada de Pedra</t>
+          <t>meia-escada de pedra</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Pilar Moderno</t>
+          <t>pilar moderno</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Pilar Moderno</t>
+          <t>pilar moderno</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Pilar Moderno</t>
+          <t>pilar moderno</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -3507,7 +3507,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Pilar Moderno</t>
+          <t>pilar moderno</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -3534,7 +3534,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Parede de Tenda</t>
+          <t>parede de tenda</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -3561,7 +3561,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Parede de Tenda</t>
+          <t>parede de tenda</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -3588,7 +3588,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Bloco de Terra Coberto Com Raízes</t>
+          <t>bloco de terra com raízes</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -3615,7 +3615,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Parede Palmeira</t>
+          <t>parede palmiana</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -3642,7 +3642,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Parede Palmeira</t>
+          <t>parede palmiana</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -3669,7 +3669,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Parede Palmeira</t>
+          <t>parede palmiana</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -3696,7 +3696,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Pilar de Tenda</t>
+          <t>pilar de tenda</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -3723,7 +3723,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Pilar de Tenda</t>
+          <t>pilar de tenda</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Pilar Palmeira</t>
+          <t>pilar palmiano</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -3777,7 +3777,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Pilar Palmeira</t>
+          <t>pilar palmiano</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -3804,7 +3804,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Pilar Palmeira</t>
+          <t>pilar palmiano</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -3831,7 +3831,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Parede Palmeira</t>
+          <t>parede palmiana</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Bloco Palmeira</t>
+          <t>bloco palmiano</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -3885,7 +3885,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Pilar de Madeira</t>
+          <t>pilar de madeira</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -3912,7 +3912,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Telhado</t>
+          <t>laje</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -3939,7 +3939,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Parede de Tijolos</t>
+          <t>parede de tijolos</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -3966,12 +3966,12 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Bloco de Editor (Invisível)</t>
+          <t>Bloco Especial (Invisível)</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Editor Block(Invisiblel)</t>
+          <t>Special Block (Invisible)</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -4008,7 +4008,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Bloco de Pedra</t>
+          <t>bloco de pedra</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Parede de Espelho</t>
+          <t>parede de espelho</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -4062,7 +4062,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Parede de Vidro</t>
+          <t>parede de vidro</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -4089,7 +4089,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Bloco de Navio</t>
+          <t>bloco de navio</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Bloco de Navio</t>
+          <t>bloco de navio</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -4143,7 +4143,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Bloco de Navio</t>
+          <t>bloco de navio</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -4170,7 +4170,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Meia-Escada de Madeiras</t>
+          <t>meia-escada de tábuas</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -4197,7 +4197,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Parede de Cassino</t>
+          <t>parede de cassino</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -4224,7 +4224,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Parede de Tijolos</t>
+          <t>parede de tijolos</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -4251,7 +4251,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Bloco de Tijolos</t>
+          <t>bloco de tijolos</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -4278,7 +4278,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Parede de Pedra</t>
+          <t>parede de pedra</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -4305,7 +4305,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Bloco de Pedra</t>
+          <t>bloco de pedra</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -4332,7 +4332,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Bloco de Decoração</t>
+          <t>bloco de decoração</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -4359,7 +4359,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Parede de Pedra</t>
+          <t>parede de pedra</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Bloco de Pedra</t>
+          <t>bloco de pedra</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -4413,7 +4413,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Parede de Grama</t>
+          <t>parede de grama</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -4440,7 +4440,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Bloco de Madeiras de Qualidade</t>
+          <t>bloco de tábuas de qualidade</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -4467,7 +4467,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Bloco de Madeiras de Qualidade</t>
+          <t>bloco de tábuas de qualidade</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Parede de Madeiras de Qualidade</t>
+          <t>parede de tábuas de qualidade</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Parede Simples</t>
+          <t>parede simples</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -4548,12 +4548,12 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Bloco de Editor (Interior)</t>
+          <t>Bloco Especial (Interno)</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Editor Block(Interior)</t>
+          <t>Special Block (Interior)</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -4575,12 +4575,12 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Bloco de Editor (Exterior)</t>
+          <t>Bloco Especial (Externo)</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Editor Block(Exterior)</t>
+          <t>Special Block (Exterior)</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -4602,7 +4602,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Bloco Simples</t>
+          <t>bloco simples</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -4629,7 +4629,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Bloco Simples</t>
+          <t>bloco simples</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -4656,7 +4656,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Cerca de Metal</t>
+          <t>cerca de metal</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -4683,7 +4683,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Escada de Madeiras</t>
+          <t>escada de tábuas</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -4710,7 +4710,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Meia-Escada de Madeiras</t>
+          <t>meia-escada de tábuas</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -4737,7 +4737,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Parede Simples</t>
+          <t>parede simples</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -4764,7 +4764,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Parede Simples</t>
+          <t>parede simples</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Parede Simples</t>
+          <t>parede simples</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -4818,7 +4818,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Escada</t>
+          <t>escada de mão</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -4845,7 +4845,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Pilar de Corda</t>
+          <t>pilar de cordas</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -4872,7 +4872,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Parede de Cassino</t>
+          <t>parede de cassino</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -4899,7 +4899,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Cerca de Engrenagem</t>
+          <t>cerca de engrenagens</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -4926,7 +4926,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Parede de Papel</t>
+          <t>parede de papel</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -4953,7 +4953,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Parede de Papel</t>
+          <t>parede de papel</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -4980,7 +4980,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Bloco de Grama</t>
+          <t>bloco de grama</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -5007,7 +5007,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Parede de Átrio</t>
+          <t>parede de átrio</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -5034,7 +5034,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Bloco de Terra Coberto Com Vinhas</t>
+          <t>bloco de terra com trepadeiras</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -5061,7 +5061,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Cachoeira</t>
+          <t>cachoeira</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -5088,7 +5088,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Parede de Madeiras</t>
+          <t>parede de tábuas</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -5115,7 +5115,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Parede de Madeiras</t>
+          <t>parede de tábuas</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -5142,7 +5142,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Bloco de Metal</t>
+          <t>bloco de metal</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -5169,7 +5169,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Escada de Esqueleto</t>
+          <t>escada de esqueletos</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -5196,7 +5196,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Escada de Esqueleto</t>
+          <t>escada de esqueletos</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -5223,7 +5223,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Escada de Prateleira</t>
+          <t>escada de prateleiras</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -5250,7 +5250,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Telhado</t>
+          <t>laje</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -5277,7 +5277,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Telhado</t>
+          <t>laje</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -5304,7 +5304,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Telhado</t>
+          <t>laje</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -5331,7 +5331,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Telhado</t>
+          <t>laje</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -5358,7 +5358,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Telhado</t>
+          <t>laje</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -5385,7 +5385,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Telhado</t>
+          <t>laje</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -5412,7 +5412,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Telhado</t>
+          <t>laje</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -5439,7 +5439,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Telhado</t>
+          <t>laje</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Telhado</t>
+          <t>laje</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -5493,7 +5493,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>telhado</t>
+          <t>laje</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -5520,7 +5520,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Cerca de Madeira</t>
+          <t>cerca de madeira</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -5547,7 +5547,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Parede Falsa (Experimental)</t>
+          <t>parede falsa(experimental)</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -5574,7 +5574,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Bloco Submarino</t>
+          <t>bloco submarino</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -5601,7 +5601,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Bloco Submarino</t>
+          <t>bloco submarino</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Bloco de Coral</t>
+          <t>bloco de coral</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -5655,7 +5655,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Cerca com Arame Farpado</t>
+          <t>cerca de arame farpado</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -5682,7 +5682,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>Bloco de Esponja</t>
+          <t>bloco desconhecido</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -5709,7 +5709,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Bloco de Chocolate</t>
+          <t>bloco de chocolate</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -5736,7 +5736,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Bloco de Pão-de-Ló</t>
+          <t>bloco de esponja</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -5763,7 +5763,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Bloco de Biscoito</t>
+          <t>bloco de bolacha</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -5790,7 +5790,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Parede de Chocolate</t>
+          <t>parede de chocolate</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -5817,7 +5817,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Bloco de Bolacha</t>
+          <t>bloco de biscoito</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -5844,7 +5844,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Parede de Bolacha</t>
+          <t>parede de biscoito</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -5871,7 +5871,7 @@
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Pilar de Chocolate</t>
+          <t>pilar de chocolate</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -5898,7 +5898,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Pilar de Bolacha</t>
+          <t>pilar de biscoito</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -6044,6 +6044,411 @@
       <c r="E207" t="inlineStr">
         <is>
           <t>石のフェンス</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>EA 23.283</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>bloco de nuvem</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>cloud block</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>雲のブロック</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>EA 23.286</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>bloco alienígena</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>alien block</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>エイリアンのブロック</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>EA 23.288</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>bloco alienígena</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>alien block</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>エイリアンのブロック</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>EA 23.289</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>parede alienígena</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>alien wall</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>エイリアンの壁</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>EA 23.289</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>parede alienígena</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>alien wall</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>エイリアンの壁</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>EA 23.289</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>parede alienígena</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>alien wall</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>エイリアンの壁</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>EA 23.289</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>pilar alienígena</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>alien pillar</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>エイリアンの柱</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>EA 23.289</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>pilar alienígena</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>alien pillar</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>エイリアンの柱</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>213</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>EA 23.289</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>pilar alienígena</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>alien pillar</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>エイリアンの柱</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>EA 23.328</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>parede treliçada</t>
+        </is>
+      </c>
+      <c r="D217" t="inlineStr">
+        <is>
+          <t>lattice wall</t>
+        </is>
+      </c>
+      <c r="E217" t="inlineStr">
+        <is>
+          <t>格子の壁</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>EA 23.328</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>pilar de madeira</t>
+        </is>
+      </c>
+      <c r="D218" t="inlineStr">
+        <is>
+          <t>wooden pillar</t>
+        </is>
+      </c>
+      <c r="E218" t="inlineStr">
+        <is>
+          <t>木の柱</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>216</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>EA 23.335</t>
+        </is>
+      </c>
+      <c r="C219" t="inlineStr">
+        <is>
+          <t>parede de pedra</t>
+        </is>
+      </c>
+      <c r="D219" t="inlineStr">
+        <is>
+          <t>stone wall</t>
+        </is>
+      </c>
+      <c r="E219" t="inlineStr">
+        <is>
+          <t>石の壁</t>
+        </is>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>EA 23.335</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>pilar de pedra</t>
+        </is>
+      </c>
+      <c r="D220" t="inlineStr">
+        <is>
+          <t>stone pillar</t>
+        </is>
+      </c>
+      <c r="E220" t="inlineStr">
+        <is>
+          <t>石の柱</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>218</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>EA 23.341</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>bloco de pedra</t>
+        </is>
+      </c>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>stone block</t>
+        </is>
+      </c>
+      <c r="E221" t="inlineStr">
+        <is>
+          <t>石のブロック</t>
+        </is>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>219</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>EA 23.344</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>meia-escada de pedra</t>
+        </is>
+      </c>
+      <c r="D222" t="inlineStr">
+        <is>
+          <t>stone half-stairs</t>
+        </is>
+      </c>
+      <c r="E222" t="inlineStr">
+        <is>
+          <t>石の半階段</t>
         </is>
       </c>
     </row>
